--- a/SensWear-V1R1-Panel/Output/Manufacturing/Assembly/Bill of Materials/Bill of Materials-SensWear_SensorPanel_V1R1.xlsx
+++ b/SensWear-V1R1-Panel/Output/Manufacturing/Assembly/Bill of Materials/Bill of Materials-SensWear_SensorPanel_V1R1.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORK\Projects\OpenRing\Hardware\SensWear-V1R1-Panel\Output\Manufacturing\Assembly\Bill of Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648511E1-50C6-4065-9DCF-6B63B6CFD5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7934356-0509-4DBF-9B74-473E0BB48B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{349CB648-EE01-46E6-862A-1FCC1A091D54}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{349CB648-EE01-46E6-862A-1FCC1A091D54}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-SensWear_Sens" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Bill of Materials-SensWear_Sens'!$1:$1</definedName>
@@ -39,9 +40,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="142">
   <si>
     <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Designator</t>
   </si>
   <si>
     <t>Comment</t>
@@ -468,7 +472,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,6 +493,25 @@
       <sz val="10"/>
       <color indexed="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFAFABAB"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -519,7 +542,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -527,11 +550,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -551,6 +592,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -558,8 +605,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{C6ED0B15-C084-4BFC-9E52-7FA8EA7B34CE}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -892,11 +940,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62187C6B-1DDC-4F55-9585-5742AB6C778E}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="65.5703125" customWidth="1"/>
     <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="44.5703125" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" customWidth="1"/>
     <col min="6" max="6" width="25.42578125" customWidth="1"/>
@@ -905,800 +953,800 @@
     <col min="9" max="9" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15.75">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="4" customFormat="1">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2">
         <v>120</v>
       </c>
       <c r="Q2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="4" customFormat="1">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P3">
         <v>60</v>
       </c>
       <c r="Q3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R3">
         <v>0.30599999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" s="4" customFormat="1">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P4">
         <v>114</v>
       </c>
       <c r="Q4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R4">
         <v>3.1463999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" s="4" customFormat="1">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" t="s">
         <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" t="s">
-        <v>31</v>
       </c>
       <c r="P5">
         <v>40</v>
       </c>
       <c r="Q5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="4" customFormat="1">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6"/>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P6">
         <v>44</v>
       </c>
       <c r="Q6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="4" customFormat="1">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" t="s">
         <v>64</v>
       </c>
-      <c r="D7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" t="s">
-        <v>67</v>
-      </c>
-      <c r="J7" t="s">
-        <v>68</v>
-      </c>
-      <c r="K7" t="s">
-        <v>63</v>
-      </c>
       <c r="L7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P7">
         <v>30</v>
       </c>
       <c r="Q7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" s="4" customFormat="1">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" t="s">
         <v>74</v>
       </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" t="s">
-        <v>73</v>
-      </c>
       <c r="L8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P8">
         <v>80</v>
       </c>
       <c r="Q8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" s="4" customFormat="1">
       <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" t="s">
         <v>84</v>
       </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" t="s">
-        <v>83</v>
-      </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P9">
         <v>10</v>
       </c>
       <c r="Q9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" s="4" customFormat="1">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
         <v>93</v>
       </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" t="s">
-        <v>92</v>
-      </c>
       <c r="H10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P10">
         <v>10</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" s="4" customFormat="1">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
         <v>102</v>
       </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>101</v>
-      </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P11">
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" s="4" customFormat="1">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
         <v>110</v>
       </c>
-      <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>109</v>
-      </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P12">
         <v>10</v>
       </c>
       <c r="Q12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" s="4" customFormat="1">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P13">
         <v>10</v>
       </c>
       <c r="Q13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" s="4" customFormat="1">
       <c r="A14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:18" s="4" customFormat="1">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
         <v>129</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-    </row>
-    <row r="15" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>128</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="G15" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:18" s="4" customFormat="1">
+      <c r="A16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-    </row>
-    <row r="16" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>128</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="1:11" s="4" customFormat="1">
+      <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
         <v>129</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-    </row>
-    <row r="17" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>134</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="G17" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1710,4 +1758,234 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F5240C-09BB-4DA4-8A29-322AFDCBD47C}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="61.85546875" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>